--- a/branches/dependabot/github_actions/dev/actions-046f3e2dc6/all-profiles.xlsx
+++ b/branches/dependabot/github_actions/dev/actions-046f3e2dc6/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-24T01:38:47+00:00</t>
+    <t>2026-08-27T19:41:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
